--- a/tests/fixtures/04_bank_statement/data-export-control.xlsx
+++ b/tests/fixtures/04_bank_statement/data-export-control.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\2026\excel\tests\fixtures\04_bank_statement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0FEFEA7-F810-4AE1-8106-482FCF8E216A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA6C12C9-B817-4F82-B184-5F58A1022047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="189" yWindow="2117" windowWidth="15651" windowHeight="13834" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33157" yWindow="1028" windowWidth="15653" windowHeight="13837" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="21">
   <si>
     <t>Jane Smith</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>txn.balance</t>
+  </si>
+  <si>
+    <t>HEADER</t>
   </si>
 </sst>
 </file>
@@ -503,12 +506,6 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
@@ -519,7 +516,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>15</v>
